--- a/submissions/2A202602457_NguyenHoangSon/results.xlsx
+++ b/submissions/2A202602457_NguyenHoangSon/results.xlsx
@@ -4013,7 +4013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -5211,6 +5211,59 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>F01 chung kết (crop5)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Tesla T4</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>fp32</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="n">
+        <v>224</v>
+      </c>
+      <c r="F23" t="n">
+        <v>5</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>26.0741185002189</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>26.84592740029075</v>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>27.83699085011904</v>
+      </c>
+      <c r="K23" s="2" t="n">
+        <v>38.35220738110877</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>2.11.0+cu128</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>không tính</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
